--- a/artfynd/A 45777-2023 artfynd.xlsx
+++ b/artfynd/A 45777-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45777-2023 artfynd.xlsx
+++ b/artfynd/A 45777-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1075,133 +1075,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>61254429</v>
-      </c>
-      <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ideboås, Sm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>542373.1072736924</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6320903.928612315</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Uppvidinge</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Älghult</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>per taube</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>per taube</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45777-2023 artfynd.xlsx
+++ b/artfynd/A 45777-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61673189</v>
+        <v>61673201</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>ideboås, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542282.0382813376</v>
+        <v>542302</v>
       </c>
       <c r="R2" t="n">
-        <v>6320904.087139552</v>
+        <v>6320978</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +753,9 @@
           <t>2016-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,8 +764,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>160 årig tall</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris # 160 årig tall</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -794,63 +808,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61673201</v>
+        <v>61673189</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>ideboås, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542302.0027780212</v>
+        <v>542282</v>
       </c>
       <c r="R3" t="n">
-        <v>6320978.305076948</v>
+        <v>6320904</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,19 +883,9 @@
           <t>2016-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,34 +894,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>160 årig tall</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris # 160 årig tall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -942,15 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90955610</v>
+        <v>61254429</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,16 +955,17 @@
           <t>i frukt</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ideboås, Sm</t>
+          <t>ideboås, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542373.1017110574</v>
+        <v>542373</v>
       </c>
       <c r="R4" t="n">
-        <v>6320904.472782933</v>
+        <v>6320904</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1024,29 +990,14 @@
           <t>Älghult</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>G-Upp-0582</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,7 +1012,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>per taube</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1069,11 +1020,7 @@
           <t>per taube</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
